--- a/self_paced_reading/experiment/StimuliSPR.xlsx
+++ b/self_paced_reading/experiment/StimuliSPR.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aldos\OneDrive\Desktop\Projects\AdjunctControl26\self_paced_reading\experiment\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aldos\OneDrive\Desktop\Projects\AdjunctControl\self_paced_reading\experiment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{233C2000-388E-4592-A1D1-7A3F9CC43425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CABAB5A-1CD8-4B35-A874-C2712F01F8C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{49F68F50-C0A0-2A43-B5F6-E3A97D82E26C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="171">
   <si>
     <t>item</t>
   </si>
@@ -62,9 +62,6 @@
     <t>critical</t>
   </si>
   <si>
-    <t xml:space="preserve">Consisting of ten passages, the author will publish a new book </t>
-  </si>
-  <si>
     <t>author</t>
   </si>
   <si>
@@ -77,21 +74,9 @@
     <t>Consisting of ten passages that she wrote, the author will publish a new book</t>
   </si>
   <si>
-    <t>Consisting of ten passages, a new book will be published by the author</t>
-  </si>
-  <si>
-    <t>Consisting of ten passages that she wrote, a new book will be published by the author </t>
-  </si>
-  <si>
-    <t>Containing all the marbles, the girl will shake the jar violently </t>
-  </si>
-  <si>
     <t>Containing all the marbles that she bought, the girl will shake the jar violently </t>
   </si>
   <si>
-    <t>Containing all the marbles, the jar will be violently shaken by the girl </t>
-  </si>
-  <si>
     <t>Containing all the marbles that she bought, the jar will be violently shaken by the girl</t>
   </si>
   <si>
@@ -104,87 +89,18 @@
     <t>girl</t>
   </si>
   <si>
-    <t>Composed of ice cream and meringue, the baker will present the baked Alaska</t>
-  </si>
-  <si>
-    <t>Composed of ice cream and meringue that she prepared, the baker will present the baked Alaska </t>
-  </si>
-  <si>
-    <t>Composed of ice cream and meringue, the baked Alaska will be presented by the baker </t>
-  </si>
-  <si>
-    <t>Composed of ice cream and meringue that she prepared, the baked Alaska will be presented by the baker </t>
-  </si>
-  <si>
     <t>baker</t>
   </si>
   <si>
-    <t>Running on clean energy, the environmentalist will love his car deeply</t>
-  </si>
-  <si>
-    <t>Running on clean energy that he harvested from solar panels, the environmentalist will love his car deeply</t>
-  </si>
-  <si>
-    <t>Running on clean energy, the car will be loved deeply by the environmentalist</t>
-  </si>
-  <si>
-    <t>Running on clean energy that he harvested from solar panels, the car will be loved deeply by the environmentalist</t>
-  </si>
-  <si>
     <t>environmentalist</t>
   </si>
   <si>
-    <t>Totaling eight athletes, the coach will manage the dedicated team</t>
-  </si>
-  <si>
-    <t>Totaling eight athletes that he recruited, the coach will manage the dedicated team</t>
-  </si>
-  <si>
-    <t>Totaling eight athletes, the dedicated team will be managed by the coach</t>
-  </si>
-  <si>
-    <t>Totaling eight athletes that he recruited, the dedicated team will be managed by the coach</t>
-  </si>
-  <si>
     <t>coach</t>
   </si>
   <si>
-    <t>Housing only international students, the girls will occupy the new dormitory for now</t>
-  </si>
-  <si>
-    <t>Housing only international students that the school accepted, the girls will occupy the new dormitory for now</t>
-  </si>
-  <si>
-    <t>Housing only international students, the new dormitory will be occupied by the girls for now</t>
-  </si>
-  <si>
-    <t>Housing only international students that the school accepted, the new dormitory will be occupied by the girls for now</t>
-  </si>
-  <si>
-    <t>girls</t>
-  </si>
-  <si>
-    <t>Spanning the peaceful countryside, the queen will rule the mountain territories </t>
-  </si>
-  <si>
-    <t>Spanning the peaceful countryside that she grew up in, the queen will rule the mountain territories</t>
-  </si>
-  <si>
-    <t>Spanning the peaceful countryside, the mountain territories will be ruled by the queen</t>
-  </si>
-  <si>
-    <t>Spanning the peaceful countryside that she grew up in, the mountain territories will be ruled by the queen</t>
-  </si>
-  <si>
-    <t>Featuring the brick oven, the chef will monitor the kitchen</t>
-  </si>
-  <si>
     <t>Featuring the brick oven that he installed last week, the chef will monitor the kitchen</t>
   </si>
   <si>
-    <t>Featuring the brick oven, the kitchen will be monitored by the chef</t>
-  </si>
-  <si>
     <t>Featuring the brick oven that he installed last week, the kitchen will be monitored by the chef</t>
   </si>
   <si>
@@ -302,18 +218,6 @@
     <t>blank</t>
   </si>
   <si>
-    <t>Derived from ancient Greek texts, the student will study the tome carefully</t>
-  </si>
-  <si>
-    <t>Derived from ancient Greek texts that she unearthed at the temple, the student will study the tome carefully</t>
-  </si>
-  <si>
-    <t>Derived from ancient Greek texts, the tome will be studied carefully by the student</t>
-  </si>
-  <si>
-    <t>Derived from ancient Greek texts that she unearthed at the temple, the tome will be studied carefully by the student</t>
-  </si>
-  <si>
     <t>student</t>
   </si>
   <si>
@@ -332,36 +236,9 @@
     <t>team</t>
   </si>
   <si>
-    <t>Alaska</t>
-  </si>
-  <si>
     <t>dormitory</t>
   </si>
   <si>
-    <t>Formed from slippery red clay, the artist will admire the handmade flowerpot </t>
-  </si>
-  <si>
-    <t>Formed from slippery red clay that he bought in New Mexico, the artist will admire the handmade flowerpot</t>
-  </si>
-  <si>
-    <t>Formed from slippery red clay, the handmade flowerpot will be admired by the artist</t>
-  </si>
-  <si>
-    <t>Formed from slippery red clay that he bought in New Mexico, the handmade flowerpot will be admired by the artist </t>
-  </si>
-  <si>
-    <t>Built from the ruins of the town hall, the salesman will market the new skyscraper</t>
-  </si>
-  <si>
-    <t>Built from the ruins of the town hall that he demolished last year, the salesman will market the new skyscraper</t>
-  </si>
-  <si>
-    <t>Built from the ruins of the town hall, the new skyscraper will be marketed by the salesman</t>
-  </si>
-  <si>
-    <t>Built from the ruins of the town hall that he demolished last year, the new skyscraper will be marketed by the salesman</t>
-  </si>
-  <si>
     <t>artist</t>
   </si>
   <si>
@@ -371,15 +248,6 @@
     <t>salesman</t>
   </si>
   <si>
-    <t>Comprising six difficult classes, the teacher will manage her busy schedule</t>
-  </si>
-  <si>
-    <t>Comprising six difficult classes that she designed herself, the teacher will manage her busy schedule</t>
-  </si>
-  <si>
-    <t>Comprising six difficult classes, the busy schedule will be managed by the teacher</t>
-  </si>
-  <si>
     <t>teacher</t>
   </si>
   <si>
@@ -546,6 +414,141 @@
   </si>
   <si>
     <t>Was the ripe banana eaten by a gopher?</t>
+  </si>
+  <si>
+    <t>Consisting of ten passages that was written, a book will be published by the author</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consisting of ten passages that was written, the author will publish a book </t>
+  </si>
+  <si>
+    <t>Consisting of ten passages that she wrote, a book will be published by the author </t>
+  </si>
+  <si>
+    <t>Containing all the marbles that was bought, the girl will shake the jar violently </t>
+  </si>
+  <si>
+    <t>Containing all the marbles that was bought, the jar will be violently shaken by the girl </t>
+  </si>
+  <si>
+    <t>dessert</t>
+  </si>
+  <si>
+    <t>Composed of meringue that was prepared, the baker will present the dessert</t>
+  </si>
+  <si>
+    <t>Composed of meringue that she prepared, the baker will present the baked Alaska </t>
+  </si>
+  <si>
+    <t>Composed of meringue that she prepared, the dessert will be presented by the baker </t>
+  </si>
+  <si>
+    <t>Composed of meringue that was prepared, the dessert will be presented by the baker </t>
+  </si>
+  <si>
+    <t>Derived from ancient Greek texts that was unearthed, the student will study the tome carefully</t>
+  </si>
+  <si>
+    <t>Derived from ancient Greek texts that she unearthed, the student will study the tome carefully</t>
+  </si>
+  <si>
+    <t>Derived from ancient Greek texts that was unearthed, the tome will be studied carefully by the student</t>
+  </si>
+  <si>
+    <t>Derived from ancient Greek texts that she unearthed, the tome will be studied carefully by the student</t>
+  </si>
+  <si>
+    <t>Formed from red clay that was bought in New Mexico, the flowerpot will be admired by the artist</t>
+  </si>
+  <si>
+    <t>Formed from red clay that he bought in New Mexico, the flowerpot will be admired by the artist </t>
+  </si>
+  <si>
+    <t>Formed from red clay that was bought in New Mexico, the artist will admire the flowerpot </t>
+  </si>
+  <si>
+    <t>Formed from red clay that he bought in New Mexico, the artist will admire the flowerpot</t>
+  </si>
+  <si>
+    <t>Built from the ruins of the town hall that was demolished, the salesman will market the new skyscraper</t>
+  </si>
+  <si>
+    <t>Built from the ruins of the town hall that he demolished, the salesman will market the new skyscraper</t>
+  </si>
+  <si>
+    <t>Built from the ruins of the town hall that he demolished, the skyscraper will be marketed by the salesman</t>
+  </si>
+  <si>
+    <t>Built from the ruins of the town hall that was demolished, the skyscraper will be marketed by the salesman</t>
+  </si>
+  <si>
+    <t>Totaling eight athletes that he recruited, the team will be managed by the coach</t>
+  </si>
+  <si>
+    <t>Totaling eight athletes that was recruited, the team will be managed by the coach</t>
+  </si>
+  <si>
+    <t>Totaling eight athletes that was recruited, the coach will manage the team</t>
+  </si>
+  <si>
+    <t>Totaling eight athletes that he recruited, the coach will manage the team</t>
+  </si>
+  <si>
+    <t>Housing only new students that were interviewed, the headmaster will visit the dormitory</t>
+  </si>
+  <si>
+    <t>Housing only new students that were interviewed, the dormitory will be visited by the headmaster</t>
+  </si>
+  <si>
+    <t>Housing only new students that he interviewed, the dormitory will be visited by the headmaster</t>
+  </si>
+  <si>
+    <t>Housing only new students that he interviewed, the headmaster will visit the dormitory</t>
+  </si>
+  <si>
+    <t>Comprising six difficult classes that were designed carefully, the schedule will be managed by the teacher</t>
+  </si>
+  <si>
+    <t>Comprising six difficult classes that she designed carefully, the schedule will be managed by the teacher</t>
+  </si>
+  <si>
+    <t>Comprising six difficult classes that she designed carefully, the teacher will manage her schedule</t>
+  </si>
+  <si>
+    <t>Comprising six difficult classes that were designed carefully, the teacher will manage her schedule</t>
+  </si>
+  <si>
+    <t>Spanning the peaceful countryside that she conquerored, the territories will be ruled by the queen</t>
+  </si>
+  <si>
+    <t>Spanning the peaceful countryside that was conquerored, the territories will be ruled by the queen</t>
+  </si>
+  <si>
+    <t>Spanning the peaceful countryside that was conquerored, the queen will rule the territories </t>
+  </si>
+  <si>
+    <t>Spanning the peaceful countryside that she conquerored, the queen will rule the territories</t>
+  </si>
+  <si>
+    <t>Featuring the brick oven that was installed last week, the kitchen will be monitored by the chef</t>
+  </si>
+  <si>
+    <t>Featuring the brick oven that was installed last week, the chef will monitor the kitchen</t>
+  </si>
+  <si>
+    <t>Running on energy that was harvested from solar panels, the car will be loved deeply by the environmentalist</t>
+  </si>
+  <si>
+    <t>Running on energy that he harvested from solar panels, the car will be loved deeply by the environmentalist</t>
+  </si>
+  <si>
+    <t>Running on energy that he harvested from solar panels, the environmentalist will love his car deeply</t>
+  </si>
+  <si>
+    <t>Running on energy that was harvested from solar panels, the environmentalist will love his car deeply</t>
+  </si>
+  <si>
+    <t>headmaster</t>
   </si>
 </sst>
 </file>
@@ -958,10 +961,10 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>117</v>
+        <v>73</v>
       </c>
       <c r="I1" t="s">
-        <v>120</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.6">
@@ -975,22 +978,22 @@
         <v>7</v>
       </c>
       <c r="D2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>10</v>
       </c>
-      <c r="G2" t="s">
-        <v>11</v>
-      </c>
       <c r="H2" t="s">
-        <v>142</v>
+        <v>98</v>
       </c>
       <c r="I2" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.6">
@@ -1004,22 +1007,22 @@
         <v>7</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
         <v>9</v>
       </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
       <c r="G3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>142</v>
+        <v>98</v>
       </c>
       <c r="I3" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.6">
@@ -1033,22 +1036,22 @@
         <v>7</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>13</v>
+        <v>126</v>
       </c>
       <c r="E4" t="s">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="F4" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H4" t="s">
-        <v>142</v>
+        <v>98</v>
       </c>
       <c r="I4" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.6">
@@ -1062,22 +1065,22 @@
         <v>7</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" t="s">
         <v>14</v>
       </c>
-      <c r="E5" t="s">
-        <v>93</v>
-      </c>
-      <c r="F5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" t="s">
-        <v>19</v>
-      </c>
       <c r="H5" t="s">
-        <v>142</v>
+        <v>98</v>
       </c>
       <c r="I5" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.6">
@@ -1091,22 +1094,22 @@
         <v>7</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>15</v>
+        <v>129</v>
       </c>
       <c r="E6" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" t="s">
         <v>10</v>
       </c>
-      <c r="G6" t="s">
-        <v>11</v>
-      </c>
       <c r="H6" t="s">
-        <v>118</v>
+        <v>74</v>
       </c>
       <c r="I6" t="s">
-        <v>146</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.6">
@@ -1120,22 +1123,22 @@
         <v>7</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" t="s">
         <v>16</v>
       </c>
-      <c r="E7" t="s">
-        <v>21</v>
-      </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H7" t="s">
-        <v>118</v>
+        <v>74</v>
       </c>
       <c r="I7" t="s">
-        <v>146</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.6">
@@ -1149,22 +1152,22 @@
         <v>7</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>17</v>
+        <v>130</v>
       </c>
       <c r="E8" t="s">
-        <v>94</v>
+        <v>62</v>
       </c>
       <c r="F8" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H8" t="s">
-        <v>118</v>
+        <v>74</v>
       </c>
       <c r="I8" t="s">
-        <v>146</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.6">
@@ -1178,22 +1181,22 @@
         <v>7</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E9" t="s">
-        <v>94</v>
+        <v>62</v>
       </c>
       <c r="F9" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G9" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H9" t="s">
-        <v>118</v>
+        <v>74</v>
       </c>
       <c r="I9" t="s">
-        <v>146</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.6">
@@ -1207,22 +1210,22 @@
         <v>7</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>22</v>
+        <v>132</v>
       </c>
       <c r="E10" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" t="s">
         <v>10</v>
       </c>
-      <c r="G10" t="s">
-        <v>11</v>
-      </c>
       <c r="H10" t="s">
-        <v>119</v>
+        <v>75</v>
       </c>
       <c r="I10" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.6">
@@ -1236,22 +1239,22 @@
         <v>7</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>23</v>
+        <v>133</v>
       </c>
       <c r="E11" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G11" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H11" t="s">
-        <v>119</v>
+        <v>75</v>
       </c>
       <c r="I11" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.6">
@@ -1265,22 +1268,22 @@
         <v>7</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>24</v>
+        <v>135</v>
       </c>
       <c r="E12" t="s">
-        <v>98</v>
+        <v>131</v>
       </c>
       <c r="F12" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H12" t="s">
-        <v>119</v>
+        <v>75</v>
       </c>
       <c r="I12" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.6">
@@ -1294,22 +1297,22 @@
         <v>7</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>25</v>
+        <v>134</v>
       </c>
       <c r="E13" t="s">
-        <v>98</v>
+        <v>131</v>
       </c>
       <c r="F13" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H13" t="s">
-        <v>119</v>
+        <v>75</v>
       </c>
       <c r="I13" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.6">
@@ -1323,22 +1326,22 @@
         <v>7</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>88</v>
+        <v>136</v>
       </c>
       <c r="E14" t="s">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="F14" t="s">
+        <v>9</v>
+      </c>
+      <c r="G14" t="s">
         <v>10</v>
       </c>
-      <c r="G14" t="s">
-        <v>11</v>
-      </c>
       <c r="H14" t="s">
-        <v>143</v>
+        <v>99</v>
       </c>
       <c r="I14" t="s">
-        <v>146</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.6">
@@ -1352,22 +1355,22 @@
         <v>7</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>89</v>
+        <v>137</v>
       </c>
       <c r="E15" t="s">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="F15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G15" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H15" t="s">
-        <v>143</v>
+        <v>99</v>
       </c>
       <c r="I15" t="s">
-        <v>146</v>
+        <v>102</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.6">
@@ -1381,22 +1384,22 @@
         <v>7</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>90</v>
+        <v>138</v>
       </c>
       <c r="E16" t="s">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="F16" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H16" t="s">
-        <v>143</v>
+        <v>99</v>
       </c>
       <c r="I16" t="s">
-        <v>146</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.6">
@@ -1410,22 +1413,22 @@
         <v>7</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>91</v>
+        <v>139</v>
       </c>
       <c r="E17" t="s">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="F17" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H17" t="s">
-        <v>143</v>
+        <v>99</v>
       </c>
       <c r="I17" t="s">
-        <v>146</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.6">
@@ -1439,22 +1442,22 @@
         <v>7</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>27</v>
+        <v>169</v>
       </c>
       <c r="E18" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F18" t="s">
+        <v>9</v>
+      </c>
+      <c r="G18" t="s">
         <v>10</v>
       </c>
-      <c r="G18" t="s">
-        <v>11</v>
-      </c>
       <c r="H18" t="s">
-        <v>121</v>
+        <v>77</v>
       </c>
       <c r="I18" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.6">
@@ -1468,22 +1471,22 @@
         <v>7</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>28</v>
+        <v>168</v>
       </c>
       <c r="E19" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F19" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G19" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H19" t="s">
-        <v>121</v>
+        <v>77</v>
       </c>
       <c r="I19" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.6">
@@ -1497,22 +1500,22 @@
         <v>7</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>29</v>
+        <v>166</v>
       </c>
       <c r="E20" t="s">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="F20" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H20" t="s">
-        <v>121</v>
+        <v>77</v>
       </c>
       <c r="I20" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.6">
@@ -1526,22 +1529,22 @@
         <v>7</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>30</v>
+        <v>167</v>
       </c>
       <c r="E21" t="s">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="F21" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H21" t="s">
-        <v>121</v>
+        <v>77</v>
       </c>
       <c r="I21" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.6">
@@ -1555,22 +1558,22 @@
         <v>7</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>100</v>
+        <v>142</v>
       </c>
       <c r="E22" t="s">
-        <v>108</v>
+        <v>67</v>
       </c>
       <c r="F22" t="s">
+        <v>9</v>
+      </c>
+      <c r="G22" t="s">
         <v>10</v>
       </c>
-      <c r="G22" t="s">
-        <v>11</v>
-      </c>
       <c r="H22" t="s">
-        <v>122</v>
+        <v>78</v>
       </c>
       <c r="I22" t="s">
-        <v>146</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.6">
@@ -1584,22 +1587,22 @@
         <v>7</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>101</v>
+        <v>143</v>
       </c>
       <c r="E23" t="s">
-        <v>108</v>
+        <v>67</v>
       </c>
       <c r="F23" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G23" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H23" t="s">
-        <v>122</v>
+        <v>78</v>
       </c>
       <c r="I23" t="s">
-        <v>146</v>
+        <v>102</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.6">
@@ -1613,22 +1616,22 @@
         <v>7</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>102</v>
+        <v>140</v>
       </c>
       <c r="E24" t="s">
-        <v>109</v>
+        <v>68</v>
       </c>
       <c r="F24" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H24" t="s">
-        <v>122</v>
+        <v>78</v>
       </c>
       <c r="I24" t="s">
-        <v>146</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.6">
@@ -1642,22 +1645,22 @@
         <v>7</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>103</v>
+        <v>141</v>
       </c>
       <c r="E25" t="s">
-        <v>109</v>
+        <v>68</v>
       </c>
       <c r="F25" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H25" t="s">
-        <v>122</v>
+        <v>78</v>
       </c>
       <c r="I25" t="s">
-        <v>146</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.6">
@@ -1671,22 +1674,22 @@
         <v>7</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>104</v>
+        <v>144</v>
       </c>
       <c r="E26" t="s">
-        <v>110</v>
+        <v>69</v>
       </c>
       <c r="F26" t="s">
+        <v>9</v>
+      </c>
+      <c r="G26" t="s">
         <v>10</v>
       </c>
-      <c r="G26" t="s">
-        <v>11</v>
-      </c>
       <c r="H26" t="s">
-        <v>123</v>
+        <v>79</v>
       </c>
       <c r="I26" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.6">
@@ -1700,22 +1703,22 @@
         <v>7</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>105</v>
+        <v>145</v>
       </c>
       <c r="E27" t="s">
-        <v>110</v>
+        <v>69</v>
       </c>
       <c r="F27" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G27" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H27" t="s">
-        <v>123</v>
+        <v>79</v>
       </c>
       <c r="I27" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.6">
@@ -1729,22 +1732,22 @@
         <v>7</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>106</v>
+        <v>147</v>
       </c>
       <c r="E28" t="s">
-        <v>116</v>
+        <v>72</v>
       </c>
       <c r="F28" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G28" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H28" t="s">
-        <v>123</v>
+        <v>79</v>
       </c>
       <c r="I28" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.6">
@@ -1758,22 +1761,22 @@
         <v>7</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="E29" t="s">
-        <v>116</v>
+        <v>72</v>
       </c>
       <c r="F29" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G29" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H29" t="s">
-        <v>123</v>
+        <v>79</v>
       </c>
       <c r="I29" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.6">
@@ -1787,22 +1790,22 @@
         <v>7</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>32</v>
+        <v>150</v>
       </c>
       <c r="E30" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="F30" t="s">
+        <v>9</v>
+      </c>
+      <c r="G30" t="s">
         <v>10</v>
       </c>
-      <c r="G30" t="s">
-        <v>11</v>
-      </c>
       <c r="H30" t="s">
-        <v>124</v>
+        <v>80</v>
       </c>
       <c r="I30" t="s">
-        <v>146</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.6">
@@ -1816,22 +1819,22 @@
         <v>7</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>33</v>
+        <v>151</v>
       </c>
       <c r="E31" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="F31" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G31" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H31" t="s">
-        <v>124</v>
+        <v>80</v>
       </c>
       <c r="I31" t="s">
-        <v>146</v>
+        <v>102</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.6">
@@ -1845,22 +1848,22 @@
         <v>7</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>34</v>
+        <v>149</v>
       </c>
       <c r="E32" t="s">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="F32" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H32" t="s">
-        <v>124</v>
+        <v>80</v>
       </c>
       <c r="I32" t="s">
-        <v>146</v>
+        <v>102</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.6">
@@ -1874,22 +1877,22 @@
         <v>7</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>35</v>
+        <v>148</v>
       </c>
       <c r="E33" t="s">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="F33" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H33" t="s">
-        <v>124</v>
+        <v>80</v>
       </c>
       <c r="I33" t="s">
-        <v>146</v>
+        <v>102</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.6">
@@ -1903,22 +1906,22 @@
         <v>7</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>37</v>
+        <v>152</v>
       </c>
       <c r="E34" t="s">
-        <v>41</v>
+        <v>170</v>
       </c>
       <c r="F34" t="s">
+        <v>9</v>
+      </c>
+      <c r="G34" t="s">
         <v>10</v>
       </c>
-      <c r="G34" t="s">
-        <v>11</v>
-      </c>
       <c r="H34" t="s">
-        <v>125</v>
+        <v>81</v>
       </c>
       <c r="I34" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.6">
@@ -1932,22 +1935,22 @@
         <v>7</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>38</v>
+        <v>155</v>
       </c>
       <c r="E35" t="s">
-        <v>41</v>
+        <v>170</v>
       </c>
       <c r="F35" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G35" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H35" t="s">
-        <v>125</v>
+        <v>81</v>
       </c>
       <c r="I35" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.6">
@@ -1961,22 +1964,22 @@
         <v>7</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>39</v>
+        <v>153</v>
       </c>
       <c r="E36" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="F36" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G36" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H36" t="s">
-        <v>125</v>
+        <v>81</v>
       </c>
       <c r="I36" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.6">
@@ -1990,22 +1993,22 @@
         <v>7</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>40</v>
+        <v>154</v>
       </c>
       <c r="E37" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="F37" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H37" t="s">
-        <v>125</v>
+        <v>81</v>
       </c>
       <c r="I37" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.6">
@@ -2019,22 +2022,22 @@
         <v>7</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>111</v>
+        <v>159</v>
       </c>
       <c r="E38" t="s">
-        <v>114</v>
+        <v>70</v>
       </c>
       <c r="F38" t="s">
+        <v>9</v>
+      </c>
+      <c r="G38" t="s">
         <v>10</v>
       </c>
-      <c r="G38" t="s">
-        <v>11</v>
-      </c>
       <c r="H38" t="s">
-        <v>144</v>
+        <v>100</v>
       </c>
       <c r="I38" t="s">
-        <v>146</v>
+        <v>102</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.6">
@@ -2048,22 +2051,22 @@
         <v>7</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>112</v>
+        <v>158</v>
       </c>
       <c r="E39" t="s">
-        <v>114</v>
+        <v>70</v>
       </c>
       <c r="F39" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G39" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H39" t="s">
-        <v>144</v>
+        <v>100</v>
       </c>
       <c r="I39" t="s">
-        <v>146</v>
+        <v>102</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.6">
@@ -2077,22 +2080,22 @@
         <v>7</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>113</v>
+        <v>156</v>
       </c>
       <c r="E40" t="s">
-        <v>115</v>
+        <v>71</v>
       </c>
       <c r="F40" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H40" t="s">
-        <v>144</v>
+        <v>100</v>
       </c>
       <c r="I40" t="s">
-        <v>146</v>
+        <v>102</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.6">
@@ -2106,22 +2109,22 @@
         <v>7</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>112</v>
+        <v>157</v>
       </c>
       <c r="E41" t="s">
-        <v>115</v>
+        <v>71</v>
       </c>
       <c r="F41" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H41" t="s">
-        <v>144</v>
+        <v>100</v>
       </c>
       <c r="I41" t="s">
-        <v>146</v>
+        <v>102</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.6">
@@ -2135,22 +2138,22 @@
         <v>7</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>42</v>
+        <v>162</v>
       </c>
       <c r="E42" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="F42" t="s">
+        <v>9</v>
+      </c>
+      <c r="G42" t="s">
         <v>10</v>
       </c>
-      <c r="G42" t="s">
-        <v>11</v>
-      </c>
       <c r="H42" t="s">
-        <v>126</v>
+        <v>82</v>
       </c>
       <c r="I42" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.6">
@@ -2164,22 +2167,22 @@
         <v>7</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>43</v>
+        <v>163</v>
       </c>
       <c r="E43" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="F43" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G43" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H43" t="s">
-        <v>126</v>
+        <v>82</v>
       </c>
       <c r="I43" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.6">
@@ -2193,22 +2196,22 @@
         <v>7</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>44</v>
+        <v>161</v>
       </c>
       <c r="E44" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="F44" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H44" t="s">
-        <v>126</v>
+        <v>82</v>
       </c>
       <c r="I44" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.6">
@@ -2222,22 +2225,22 @@
         <v>7</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>45</v>
+        <v>160</v>
       </c>
       <c r="E45" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="F45" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H45" t="s">
-        <v>126</v>
+        <v>82</v>
       </c>
       <c r="I45" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.6">
@@ -2251,22 +2254,22 @@
         <v>7</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>46</v>
+        <v>165</v>
       </c>
       <c r="E46" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="F46" t="s">
+        <v>9</v>
+      </c>
+      <c r="G46" t="s">
         <v>10</v>
       </c>
-      <c r="G46" t="s">
-        <v>11</v>
-      </c>
       <c r="H46" t="s">
-        <v>127</v>
+        <v>83</v>
       </c>
       <c r="I46" t="s">
-        <v>146</v>
+        <v>102</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.6">
@@ -2280,22 +2283,22 @@
         <v>7</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="E47" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="F47" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G47" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H47" t="s">
-        <v>127</v>
+        <v>83</v>
       </c>
       <c r="I47" t="s">
-        <v>146</v>
+        <v>102</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.6">
@@ -2309,22 +2312,22 @@
         <v>7</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>48</v>
+        <v>164</v>
       </c>
       <c r="E48" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="F48" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H48" t="s">
-        <v>127</v>
+        <v>83</v>
       </c>
       <c r="I48" t="s">
-        <v>146</v>
+        <v>102</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.6">
@@ -2338,22 +2341,22 @@
         <v>7</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="E49" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="F49" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H49" t="s">
-        <v>127</v>
+        <v>83</v>
       </c>
       <c r="I49" t="s">
-        <v>146</v>
+        <v>102</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.6">
@@ -2364,19 +2367,19 @@
         <v>1001</v>
       </c>
       <c r="C50" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>147</v>
+        <v>103</v>
       </c>
       <c r="E50" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="H50" t="s">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="I50" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.6">
@@ -2387,19 +2390,19 @@
         <v>1002</v>
       </c>
       <c r="C51" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>161</v>
+        <v>117</v>
       </c>
       <c r="E51" t="s">
-        <v>167</v>
+        <v>123</v>
       </c>
       <c r="H51" t="s">
-        <v>160</v>
+        <v>116</v>
       </c>
       <c r="I51" t="s">
-        <v>146</v>
+        <v>102</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.6">
@@ -2410,19 +2413,19 @@
         <v>1003</v>
       </c>
       <c r="C52" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>148</v>
+        <v>104</v>
       </c>
       <c r="E52" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="H52" t="s">
-        <v>159</v>
+        <v>115</v>
       </c>
       <c r="I52" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.6">
@@ -2433,19 +2436,19 @@
         <v>1004</v>
       </c>
       <c r="C53" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>149</v>
+        <v>105</v>
       </c>
       <c r="E53" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="H53" t="s">
-        <v>169</v>
+        <v>125</v>
       </c>
       <c r="I53" t="s">
-        <v>146</v>
+        <v>102</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.6">
@@ -2456,19 +2459,19 @@
         <v>1005</v>
       </c>
       <c r="C54" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>150</v>
+        <v>106</v>
       </c>
       <c r="E54" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="H54" t="s">
-        <v>162</v>
+        <v>118</v>
       </c>
       <c r="I54" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.6">
@@ -2479,19 +2482,19 @@
         <v>1006</v>
       </c>
       <c r="C55" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>151</v>
+        <v>107</v>
       </c>
       <c r="E55" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="H55" t="s">
-        <v>129</v>
+        <v>85</v>
       </c>
       <c r="I55" t="s">
-        <v>146</v>
+        <v>102</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.6">
@@ -2502,19 +2505,19 @@
         <v>1007</v>
       </c>
       <c r="C56" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>152</v>
+        <v>108</v>
       </c>
       <c r="E56" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="H56" t="s">
-        <v>163</v>
+        <v>119</v>
       </c>
       <c r="I56" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.6">
@@ -2525,19 +2528,19 @@
         <v>1008</v>
       </c>
       <c r="C57" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>153</v>
+        <v>109</v>
       </c>
       <c r="E57" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="H57" t="s">
-        <v>168</v>
+        <v>124</v>
       </c>
       <c r="I57" t="s">
-        <v>146</v>
+        <v>102</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.6">
@@ -2548,19 +2551,19 @@
         <v>1009</v>
       </c>
       <c r="C58" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>154</v>
+        <v>110</v>
       </c>
       <c r="E58" t="s">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="H58" t="s">
-        <v>164</v>
+        <v>120</v>
       </c>
       <c r="I58" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.6">
@@ -2571,19 +2574,19 @@
         <v>1010</v>
       </c>
       <c r="C59" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>155</v>
+        <v>111</v>
       </c>
       <c r="E59" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="H59" t="s">
-        <v>165</v>
+        <v>121</v>
       </c>
       <c r="I59" t="s">
-        <v>146</v>
+        <v>102</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.6">
@@ -2594,19 +2597,19 @@
         <v>1011</v>
       </c>
       <c r="C60" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>156</v>
+        <v>112</v>
       </c>
       <c r="E60" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="H60" t="s">
-        <v>166</v>
+        <v>122</v>
       </c>
       <c r="I60" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.6">
@@ -2617,19 +2620,19 @@
         <v>1012</v>
       </c>
       <c r="C61" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>157</v>
+        <v>113</v>
       </c>
       <c r="E61" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="H61" t="s">
-        <v>130</v>
+        <v>86</v>
       </c>
       <c r="I61" t="s">
-        <v>146</v>
+        <v>102</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.6">
@@ -2640,19 +2643,19 @@
         <v>1013</v>
       </c>
       <c r="C62" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="E62" t="s">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="H62" t="s">
-        <v>131</v>
+        <v>87</v>
       </c>
       <c r="I62" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.6">
@@ -2663,19 +2666,19 @@
         <v>1014</v>
       </c>
       <c r="C63" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="E63" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="H63" t="s">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="I63" t="s">
-        <v>146</v>
+        <v>102</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.6">
@@ -2686,19 +2689,19 @@
         <v>1015</v>
       </c>
       <c r="C64" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="E64" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="H64" t="s">
-        <v>133</v>
+        <v>89</v>
       </c>
       <c r="I64" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.6">
@@ -2709,19 +2712,19 @@
         <v>1016</v>
       </c>
       <c r="C65" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E65" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="H65" t="s">
-        <v>134</v>
+        <v>90</v>
       </c>
       <c r="I65" t="s">
-        <v>146</v>
+        <v>102</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.6">
@@ -2732,19 +2735,19 @@
         <v>1017</v>
       </c>
       <c r="C66" t="s">
+        <v>24</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E66" t="s">
         <v>52</v>
       </c>
-      <c r="D66" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E66" t="s">
-        <v>80</v>
-      </c>
       <c r="H66" t="s">
-        <v>135</v>
+        <v>91</v>
       </c>
       <c r="I66" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.6">
@@ -2755,19 +2758,19 @@
         <v>1018</v>
       </c>
       <c r="C67" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="E67" t="s">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="H67" t="s">
-        <v>128</v>
+        <v>84</v>
       </c>
       <c r="I67" t="s">
-        <v>146</v>
+        <v>102</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.6">
@@ -2778,19 +2781,19 @@
         <v>1019</v>
       </c>
       <c r="C68" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="E68" t="s">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="H68" t="s">
-        <v>136</v>
+        <v>92</v>
       </c>
       <c r="I68" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.6">
@@ -2801,19 +2804,19 @@
         <v>1020</v>
       </c>
       <c r="C69" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="E69" t="s">
-        <v>83</v>
+        <v>55</v>
       </c>
       <c r="H69" t="s">
-        <v>137</v>
+        <v>93</v>
       </c>
       <c r="I69" t="s">
-        <v>146</v>
+        <v>102</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.6">
@@ -2824,19 +2827,19 @@
         <v>1021</v>
       </c>
       <c r="C70" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="E70" t="s">
-        <v>84</v>
+        <v>56</v>
       </c>
       <c r="H70" t="s">
-        <v>138</v>
+        <v>94</v>
       </c>
       <c r="I70" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.6">
@@ -2847,19 +2850,19 @@
         <v>1022</v>
       </c>
       <c r="C71" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="E71" t="s">
-        <v>85</v>
+        <v>57</v>
       </c>
       <c r="H71" t="s">
-        <v>139</v>
+        <v>95</v>
       </c>
       <c r="I71" t="s">
-        <v>146</v>
+        <v>102</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.6">
@@ -2870,19 +2873,19 @@
         <v>1023</v>
       </c>
       <c r="C72" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="E72" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="H72" t="s">
-        <v>140</v>
+        <v>96</v>
       </c>
       <c r="I72" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.6">
@@ -2893,19 +2896,19 @@
         <v>1024</v>
       </c>
       <c r="C73" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="E73" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="H73" t="s">
-        <v>141</v>
+        <v>97</v>
       </c>
       <c r="I73" t="s">
-        <v>146</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
